--- a/testing/heart_rate_test.xlsx
+++ b/testing/heart_rate_test.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/arshsingh/Desktop/Spring_2025/BME_554/ecg-temp-ble-project/testing/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C290DDC2-07E1-5942-8D8C-CAE56A08005B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A8BB68B-06BF-E342-A72D-8732FBA7F3C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="500" windowWidth="35840" windowHeight="21900" xr2:uid="{8D5B9E72-2D55-AE44-8E46-EFAB4712463E}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="9">
   <si>
     <t>Heart Rate (BPM)</t>
   </si>
@@ -60,6 +60,9 @@
   </si>
   <si>
     <t>Oscilloscope Output</t>
+  </si>
+  <si>
+    <t>Bluetooth Output</t>
   </si>
 </sst>
 </file>
@@ -437,21 +440,24 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E3B5A04-C95C-5D4D-86D9-C4B3DF5CABE7}">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:R7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.2">
       <c r="B1" t="s">
         <v>6</v>
       </c>
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="N1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -485,8 +491,23 @@
       <c r="L2" t="s">
         <v>5</v>
       </c>
+      <c r="N2" t="s">
+        <v>1</v>
+      </c>
+      <c r="O2" t="s">
+        <v>2</v>
+      </c>
+      <c r="P2" t="s">
+        <v>3</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>4</v>
+      </c>
+      <c r="R2" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A3">
         <v>40</v>
       </c>
@@ -520,8 +541,23 @@
       <c r="L3">
         <v>40</v>
       </c>
+      <c r="N3">
+        <v>40</v>
+      </c>
+      <c r="O3">
+        <v>40</v>
+      </c>
+      <c r="P3">
+        <v>40</v>
+      </c>
+      <c r="Q3">
+        <v>40</v>
+      </c>
+      <c r="R3">
+        <v>40</v>
+      </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A4">
         <v>60</v>
       </c>
@@ -555,8 +591,23 @@
       <c r="L4">
         <v>60</v>
       </c>
+      <c r="N4">
+        <v>60</v>
+      </c>
+      <c r="O4">
+        <v>60</v>
+      </c>
+      <c r="P4">
+        <v>56</v>
+      </c>
+      <c r="Q4">
+        <v>58</v>
+      </c>
+      <c r="R4">
+        <v>60</v>
+      </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A5">
         <v>120</v>
       </c>
@@ -590,8 +641,23 @@
       <c r="L5">
         <v>120</v>
       </c>
+      <c r="N5">
+        <v>120</v>
+      </c>
+      <c r="O5">
+        <v>120</v>
+      </c>
+      <c r="P5">
+        <v>128</v>
+      </c>
+      <c r="Q5">
+        <v>120</v>
+      </c>
+      <c r="R5">
+        <v>120</v>
+      </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A6">
         <v>150</v>
       </c>
@@ -625,8 +691,23 @@
       <c r="L6">
         <v>150</v>
       </c>
+      <c r="N6">
+        <v>150</v>
+      </c>
+      <c r="O6">
+        <v>150</v>
+      </c>
+      <c r="P6">
+        <v>150</v>
+      </c>
+      <c r="Q6">
+        <v>150</v>
+      </c>
+      <c r="R6">
+        <v>150</v>
+      </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>180</v>
       </c>
@@ -658,6 +739,21 @@
         <v>180</v>
       </c>
       <c r="L7">
+        <v>180</v>
+      </c>
+      <c r="N7">
+        <v>182</v>
+      </c>
+      <c r="O7">
+        <v>180</v>
+      </c>
+      <c r="P7">
+        <v>172</v>
+      </c>
+      <c r="Q7">
+        <v>178</v>
+      </c>
+      <c r="R7">
         <v>180</v>
       </c>
     </row>
